--- a/tools/bbxm-risk-dashboard/data/冰冰小美风险提示.xlsx
+++ b/tools/bbxm-risk-dashboard/data/冰冰小美风险提示.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -453,6 +453,92 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>[自动分析｜冰冰小美每日任务]
+【R1】超跌修复不等于风险解除：超跌反弹主要来自空头回补，宏观风险和海力士事件窗口均未解除（来源：https://xueqiu.com/7143769715/398994022）
+【R2】外围风险未解除且海外链加速下跌：外围风险与海外链弱承接共同压制创业板，光模块和 PCB 仍在加速释放风险（来源：https://xueqiu.com/7143769715/399050245）
+【R2】K 型分化后资产配置功能失灵：新老方向同步下跌并伴随杠杆出清和多杀多，市场资产配置与逻辑定价功能失灵（来源：https://xueqiu.com/7143769715/399054118）
+【R1】日本债市与伊朗石油制裁风险同时升温：日本长期利率上行与伊朗石油制裁收紧同时出现，构成外部利率和能源风险观察节点（来源：https://xueqiu.com/7143769715/399080600）
+【R3】原油、美债、美元与汇率风险共振：油价、长端利率、美元、汇率和半导体预期同步恶化，形成多因子外部风险共振（来源：https://xueqiu.com/7143769715/399084502）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>[自动分析｜冰冰小美每日任务]
+【R2】江淮汽车盈利与交付假设被下修：销量、盈利和估值底线假设同时下修，并出现减持与流动性挤压，个股基本面风险明显增强（来源：https://xueqiu.com/7143769715/399150304）
+【R1】海外科技链仍是风险聚集地：海外链连续高开低走显示承接不足，风险继续向海外映射方向聚集（来源：https://xueqiu.com/7143769715/399198641）
+【R2】宏观不利数据增加并触发流动性抢跑：宏观不确定性和流动性抢跑共同推动无逻辑普跌，市场风险从背景传导到个股（来源：https://xueqiu.com/7143769715/399204052）
+【R2】光链下跌向权重和指数扩散：光链承接失败已向指数、锂电和基金赎回链扩散，形成流动性负反馈（来源：https://xueqiu.com/7143769715/399206908）
+【R3】创业板深跌与宏观事件窗口共振：指数深跌、恐慌、承接不足与多个未落地宏观节点同时存在，形成强风险共振（来源：https://xueqiu.com/7143769715/399211047）
+【R2】海力士再定价压制全球存储估值：海力士跨市场再定价可能触发资金迁移、存储估值压缩和金融杠杆退散（来源：https://xueqiu.com/7143769715/399224670）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>[自动分析｜冰冰小美每日任务]
+【R1】碳酸锂期货下跌压制锂矿：碳酸锂期货下行已传导到锂矿价格与估值预期，形成弱风险观察节点（来源：https://xueqiu.com/7143769715/399435048）
+【R2】海力士事件触发光链资金逃离：海力士不确定性已触发海外链资金逃离，并通过光模块权重向创业板扩散（来源：https://xueqiu.com/7143769715/399484210）
+【R1】海外光链不确定性通过权重放大指数波动：海外光链的不确定性通过高权重结构放大指数波动，形成结构性风险提示（来源：https://xueqiu.com/7143769715/399491151）
+【R3】创业板空头趋势与宏观风险共振：指数空头趋势、权重砸盘、美债红线和未落地事件同时存在，构成强风险共振（来源：https://xueqiu.com/7143769715/399510266）
+【R3】光、PCB 与锂电缺少接力形成做空集中地：光、PCB 和锂电同时缺少资金接力，套牢兑现与权重砸盘形成多板块负反馈（来源：https://xueqiu.com/7143769715/399521115）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>10</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>[自动分析｜冰冰小美每日任务]
+【R2】情绪砸盘扼杀科技反弹并拖累指数：板块切换通过情绪砸盘向科技和指数传导，形成可观察的结构性风险（来源：https://xueqiu.com/7143769715/399978181）
+【R1】科技内部快速切线放大方向脆弱性：科技内部的快速轮动说明方向承接脆弱，构成局部结构性风险提示（来源：https://xueqiu.com/7143769715/399984015）
+【R2】同质化策略与快轮动形成明显亏钱效应：策略同质化和弱修复共同加剧交易层面的亏钱效应，属于可验证的结构性风险（来源：https://xueqiu.com/7143769715/399991390）
+【R1】热钱驱动的资源品定价缺少基本面锚：资源品上涨被热钱而非稳定盈利锚主导，形成局部定价和回撤风险（来源：https://xueqiu.com/7143769715/399994056）
+【R2】市场失去定价锚并进入双向收割：缺少定价锚导致方向反复和双向亏损，构成市场结构性风险（来源：https://xueqiu.com/7143769715/400001099）
+【R3】弱承接、量化轮动与宏观风险形成共振：微观承接失败、存量轮动和未解除的宏观风险同时出现，构成强风险共振（来源：https://xueqiu.com/7143769715/400007082）
+【R2】美债收益率突破风险线要求控制仓位：长端利率越过明确风险线并直接映射到仓位控制，构成可执行的结构性风险提示（来源：https://xueqiu.com/7143769715/400012596）
+【R1】科技砸盘与石油拉升同步触发轮动恐慌：科技与石油在同一时点反向波动，揭示事件驱动的局部风险切换（来源：https://xueqiu.com/7143769715/400015915）
+【R2】韩国科技波动成为国内科技的量化传导锚：海外价格通过量化策略快速传导至国内科技，形成跨市场结构性风险（来源：https://xueqiu.com/7143769715/400022325）
+【R1】美元潮汐与密集事件维持防守环境：美元潮汐尚未完全退场且事件窗口密集，构成总体层面的风险候选提示（来源：https://xueqiu.com/7143769715/400047102）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tools/bbxm-risk-dashboard/data/冰冰小美风险提示.xlsx
+++ b/tools/bbxm-risk-dashboard/data/冰冰小美风险提示.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -539,6 +539,26 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>[自动分析｜冰冰小美每日任务]
+【R2】市场恐慌跌破下跌趋势通道：作者直接提示市场恐慌和趋势破位，说明情绪与承接风险仍在释放，属于风险增强节点。（来源：https://xueqiu.com/7143769715/400749999）
+【R3】海力士ADR做空引发亚太恐慌：作者给出外部做空、日韩恐慌和A股资金防守切换的完整链条，属于跨市场风险增强节点。（来源：https://xueqiu.com/7143769715/400757028）
+【W1】超卖修正是改善市场契机：作者把当日参与限定为基于偏离的修正，并明确不是抄底，属于早期风险转弱或修复观察节点。（来源：https://xueqiu.com/7143769715/400764612）
+【R3】日韩科技行情极端回撤需重新来过：作者明确描述杠杆放大、结构恶化、踩踏恐慌和市场推倒重来，属于强风险增强节点。（来源：https://xueqiu.com/7143769715/400768917）
+【R3】米相关不利叠加量化收割波动：作者把多个外部变量与A股量化波动收割连接，形成宏观、跨市场和交易结构叠加的风险增强节点。（来源：https://xueqiu.com/7143769715/400772830）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tools/bbxm-risk-dashboard/data/冰冰小美风险提示.xlsx
+++ b/tools/bbxm-risk-dashboard/data/冰冰小美风险提示.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -559,6 +559,26 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>[自动分析｜冰冰小美每日任务]
+【R2】市场无效与做空风险：该帖提供市场无效到宏观做空风险的框架性传导，属于风险识别和风险增强观察节点。（来源：https://xueqiu.com/7143769715/401053971）
+【R2】救市锚定低估值高股息：作者描述科技链风险未解除、资金转向防守锚，属于科技高弹性方向的风险增强节点。（来源：https://xueqiu.com/7143769715/401072791）
+【W1】高股息更适合均衡配置：该帖不是新增进攻信号，而是提示低估值高股息对组合波动的防守承接，属于早期风险缓和观察。（来源：https://xueqiu.com/7143769715/401078757）
+【R2】量化锚定亚太导致科技链下行：作者明确指出外部锚和量化策略未变，科技链下行风险仍在传导。（来源：https://xueqiu.com/7143769715/401085882）
+【R3】救市难改科技流动性瓦解：该帖给出救市无效、信心受挫、赎回去杠杆和流动性瓦解的完整链条，属于强风险增强节点。（来源：https://xueqiu.com/7143769715/401090815）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tools/bbxm-risk-dashboard/data/冰冰小美风险提示.xlsx
+++ b/tools/bbxm-risk-dashboard/data/冰冰小美风险提示.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -579,6 +579,34 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>13</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>[自动分析｜冰冰小美每日任务]
+【R1】医药科技跷跷板仍在：早盘挤压没有完全解除，属于弱风险观察。（来源：https://xueqiu.com/7143769715/401305543）
+【W1】全A加速点触发修正行情：风险从扩散开始边际缓和，但作者仍定位为修正行情。（来源：https://xueqiu.com/7143769715/401351183）
+【R2】极端反弹一次到位：反弹太快会降低短线后续买入的风险收益比。（来源：https://xueqiu.com/7143769715/401353656）
+【W1】老登同涨确认修正质量：这是跷跷板风险减弱的早期确认条件。（来源：https://xueqiu.com/7143769715/401359951）
+【R1】七月暴露贪婪恐惧黑暗面：情绪风险仍在，但这条更多是风险教育而非新增交易信号。（来源：https://xueqiu.com/7143769715/401363192）
+【W2】修正行情确认牛熊边界：风险释放进入关键确认阶段，较早盘恐慌已有实质缓和。（来源：https://xueqiu.com/7143769715/401364828）
+【W1】科技仓位均衡优先于做T：风险处理从恐慌割肉转为组合纪律，属于弱化但仍需约束。（来源：https://xueqiu.com/7143769715/401373870）
+【W1】医药回升是好现象：单条证据较短，但与全天跷跷板框架一致。（来源：https://xueqiu.com/7143769715/401382109）
+【W2】非科技韧性决定挤压减弱：这是当天确认风险转弱的关键验证项。（来源：https://xueqiu.com/7143769715/401382526）
+【W1】合理分化胜过极端跷跷板：风险转弱的条件从完全同涨修正为合理分化。（来源：https://xueqiu.com/7143769715/401383632）
+【W2】有色趋势未被风险打断：有色方向从被风险扰动转向趋势修复确认。（来源：https://xueqiu.com/7143769715/401390361）
+【R2】科技地板买入仍属极端行情：风险修复伴随极端波动，短线风险仍高。（来源：https://xueqiu.com/7143769715/401401234）
+【W3】国产算力交换机承载修正情绪标：多项风险转弱条件同日共振，是当天最高等级的修复信号，但仍需次日接力验证。（来源：https://xueqiu.com/7143769715/401405319）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tools/bbxm-risk-dashboard/data/冰冰小美风险提示.xlsx
+++ b/tools/bbxm-risk-dashboard/data/冰冰小美风险提示.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -607,6 +607,27 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>6</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>[自动分析｜冰冰小美每日任务]
+【W1】小作文利空后的卖盘松动与国产链承接：这是风险边际转弱节点，而不是确定趋势反转；证据集中在卖盘松动和国产链承接。（来源：https://xueqiu.com/7143769715/403716131）
+【W1】宏观风险减弱对仓位约束边际放松：宏观压力边际减弱，但仍需竞争格局、流动性和情绪位置同步确认。（来源：https://xueqiu.com/7143769715/403718539）
+【W1】成长一致性降温后的修复分歧：这是成长拥挤风险边际释放信号，但跷跷板仍限制风险等级。（来源：https://xueqiu.com/7143769715/403721411）
+【W2】创业板承接增强与宏观减弱节点：多个市场行为信号共同指向风险明确转弱，但外围信息仍会造成情绪波动。（来源：https://xueqiu.com/7143769715/403734620）
+【R1】上方阻力与跷跷板结构仍压制修复：这是弱风险观察节点，用于提醒修复行情上方阻力和结构不健康。（来源：https://xueqiu.com/7143769715/403742903）
+【W1】铜资源资产增厚与冶金盈利改善：产业与基本面风险边际转弱，适合记录为资源方向机会节点。（来源：https://xueqiu.com/7143769715/403800230）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tools/bbxm-risk-dashboard/data/冰冰小美风险提示.xlsx
+++ b/tools/bbxm-risk-dashboard/data/冰冰小美风险提示.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -628,6 +628,24 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>[自动分析｜冰冰小美每日任务]
+【R1】量化市场与通胀线、科技线跷跷板：量化高抛低吸和尾盘科技线拉动反复出现，说明微观流动性和情绪结构不稳定；作者仍把通胀线作为主线，提示科技线追涨回落风险。（来源：https://xueqiu.com/7143769715/406004910）
+【R2】美债利率干预与通胀线趋势增强：美债利率干预有效期短、石油危机后置和通胀抬头被作者串成同一条传导链，指向通胀线增强与科技线交易扰动，属于宏观风险继续增强观察。（来源：https://xueqiu.com/7143769715/406016674）
+【R2】美国财政约束、美债利息与全球风险传导：该帖形成完整宏观风险链：美债利息压力上升会挤压财政空间，并通过缩表、战争/国防、关税、金融收割、稳定币/比特币、AI发债和美联储容忍度调整传导到美股与全球市场。（来源：https://xueqiu.com/7143769715/406026359）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
